--- a/tabelas_classes_excel/Tabela_3-6_O_Clérigo.xlsx
+++ b/tabelas_classes_excel/Tabela_3-6_O_Clérigo.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -681,31 +681,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -717,272 +692,347 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bônus Base de</t>
+          <t>Nível</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bônus Base de Ataque</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reflexos</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vontade</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Especial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nível</t>
+          <t>1°</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ataque</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fortitude</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reflexos</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vontade Especial</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Expulsar ou fascinar | 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Expulsar ou fascinar</t>
+          <t>2°</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1°</t>
+          <t>3°</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mortos-vivos</t>
+          <t>4°</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2°</t>
+          <t>5°</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3°</t>
+          <t>6°</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4°</t>
+          <t>7°</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5°</t>
+          <t>8°</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6°</t>
+          <t>9°</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7°</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7/+2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -994,27 +1044,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>11°</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+8/+3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1026,27 +1076,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9°</t>
+          <t>12°</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1058,27 +1108,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>13°</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>+7/+2</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1090,27 +1140,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11°</t>
+          <t>14°</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+8/+3</t>
+          <t>+10/+5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1122,27 +1172,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12°</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+11/+6/+1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1154,27 +1204,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13°</t>
+          <t>16°</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+12/+7/+2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1186,27 +1236,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14°</t>
+          <t>17°</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>+10/+5</t>
+          <t>+12/+7/+2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1218,27 +1268,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>18°</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+11/+6/+1</t>
+          <t>+13/+8/+3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1250,27 +1300,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16°</t>
+          <t>19°</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+12/+7/+2</t>
+          <t>+14/+9/+4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1282,142 +1332,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17°</t>
+          <t>20°</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+12/+7/+2</t>
+          <t>+15/+10/+5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>18°</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>+13/+8/+3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>19°</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>+14/+9/+4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20°</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>+15/+10/+5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>* Além da quantidade indicada de magias por dia entre o 1° e o 9° nível, um clérigo recebe uma magia adicional de domíni</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>de domínio não são consideradas nas magias adicionais que o clérigo receberia devido a um valor elevado de Sabedoria.</t>
         </is>
       </c>
     </row>
